--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gitHome\pingdingshan\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="108" windowWidth="19392" windowHeight="7092"/>
+    <workbookView xWindow="600" yWindow="110" windowWidth="19400" windowHeight="7100"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="563">
+  <si>
+    <t>发起机构代码</t>
+  </si>
   <si>
     <t>产品种类</t>
   </si>
@@ -91,10 +99,6 @@
   </si>
   <si>
     <t>产品对应资产池代码</t>
-  </si>
-  <si>
-    <t>募集资金币种</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>兑付本金币种</t>
@@ -196,18 +200,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>客户类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>${data.customerType}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>增信机构类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>${data.creditType}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -367,6 +363,9 @@
     <t>青海省</t>
   </si>
   <si>
+    <t>宁夏</t>
+  </si>
+  <si>
     <t>新疆维吾尔自治区</t>
   </si>
   <si>
@@ -382,6 +381,77 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>样式：文本
+内容：中文名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">样式：文本
+</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：公募、私募</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：单独管理、集合管理</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：开放式净值型、开放式非净值型、封闭式净值型、封闭式非净值型</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：表内存款、表内非存款负债、表外</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：是、否</t>
+  </si>
+  <si>
+    <t>日期格式：YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>选项：有、无</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：有、无</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：14位代码</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+如果有多个选项，使用&amp;分隔</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+选项：单位，个人，个人及单位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+如果有多个选项，使用&amp;分隔      选项：广义政府&amp;非金融性公司&amp;金融性公司&amp;住户部门&amp;国外部门</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称
+如果有多个选项，使用&amp;分隔      选项：内部增级&amp;外部增级</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：主动管理业务、被动管理业务</t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：独立运作、银信合作、银保合作、银基合作、银证合作、混合类、其他、不适用</t>
+  </si>
+  <si>
     <t>产品基本信息:</t>
   </si>
   <si>
@@ -424,6 +494,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>资金信托计划</t>
@@ -459,6 +530,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>是</t>
@@ -480,6 +552,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品增信机构类型，产品增信形式</t>
@@ -496,6 +569,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必填</t>
@@ -517,6 +591,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>否</t>
@@ -538,6 +613,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品增信机构类型，产品增信形式</t>
@@ -554,6 +630,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必须为空</t>
@@ -575,6 +652,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>表外</t>
@@ -596,6 +674,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品对应的资产池代码</t>
@@ -612,6 +691,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必填</t>
@@ -633,6 +713,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>非表外</t>
@@ -654,6 +735,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品对应的资产池代码</t>
@@ -670,6 +752,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必须为空</t>
@@ -697,6 +780,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>募集起始日期</t>
@@ -718,6 +802,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>募集结束日期</t>
@@ -742,6 +827,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品起始日期</t>
@@ -766,6 +852,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>预计客户最低年收益率</t>
@@ -788,6 +875,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>币种需要使用中文名称</t>
@@ -804,6 +892,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>多币种间用</t>
@@ -820,6 +909,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>分割。</t>
@@ -833,6 +923,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>收益率需要直接提供</t>
@@ -849,6 +940,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>前数值，例如</t>
@@ -865,6 +957,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，那么直接提供</t>
@@ -881,6 +974,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不要带</t>
@@ -897,6 +991,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，如果带</t>
@@ -913,6 +1008,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>号数据会缩小</t>
@@ -929,6 +1025,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>倍。</t>
@@ -942,6 +1039,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -963,6 +1061,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>个币种的人民币合计必填。</t>
@@ -984,6 +1083,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>各省的和；人民币合计</t>
@@ -1000,6 +1100,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>人民币金额</t>
@@ -1016,6 +1117,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>外币的转人民币金额</t>
@@ -1052,6 +1154,7 @@
         <b/>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>导入文件（产品基本信息）的命名规则：</t>
@@ -1065,6 +1168,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -1081,6 +1185,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“</t>
@@ -1097,6 +1202,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”</t>
@@ -1118,6 +1224,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -1134,6 +1241,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>文件命名规则：</t>
@@ -1150,6 +1258,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“</t>
@@ -1166,6 +1275,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”每个</t>
@@ -1182,6 +1292,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>只包含单一产品信息，压缩文件中的文件为</t>
@@ -1198,6 +1309,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>格式，</t>
@@ -1214,6 +1326,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>文件名中不能包含中文字符。</t>
@@ -1235,6 +1348,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单元格样式为文本处理的，如果不是文本</t>
@@ -1251,6 +1365,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>系统会报错。请在录入数据前将</t>
@@ -1267,6 +1382,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单元格样式设置好后再录入数据。</t>
@@ -2449,27 +2565,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宁夏回族自治区</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>发起机构代码</t>
+    <t>不能修改模板样式，表头从第2行开始；
+第一个sheet页不能删除列
+募集资金币种、兑付本金币种、兑付收益币种、客户类型、增信机构类型、增信形式如果有多个选项，使用&amp;分隔；
+起始募集信息，客户类型和募集币种，根据基本信息中的信息自行选择，将不需要的删除掉，需要增加的按照样式增加；
+数据填写使用中文名称；
+一个excel文件只能导入一只产品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">样式：文本
+选项：理财产品、资金信托计划 </t>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：固定收益类、权益类、商品及金融衍生品类、混合类、表内</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>发起机构名称</t>
+    <t>样式：文本
+内容：中文名称  选项：商业银行发行、理财子公司发行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>${data.issuePartyName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>募集资金币种</t>
+  </si>
+  <si>
+    <t>客户类型</t>
+  </si>
+  <si>
+    <t>增信机构类型</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2480,28 +2611,20 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2511,19 +2634,28 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2540,6 +2672,7 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2549,25 +2682,11 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2578,9 +2697,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -2644,74 +2781,65 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -2720,38 +2848,56 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2763,12 +2909,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2810,7 +2959,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2845,7 +2994,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3054,242 +3203,349 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL2"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="18.44140625" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="15.6640625" style="5"/>
+    <col min="1" max="1" width="18.453125" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="15.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="2" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:37" customFormat="1" ht="249.75" customHeight="1">
+      <c r="A1" s="32" t="s">
+        <v>556</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>557</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="P1" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q1" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="S1" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="T1" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="U1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="W1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="X1" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y1" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z1" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB1" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC1" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD1" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE1" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF1" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG1" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH1" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI1" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ1" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK1" s="33" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" s="37" customFormat="1" ht="26" customHeight="1">
+      <c r="A2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E2" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I2" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K2" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M2" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N2" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O2" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P2" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q2" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="S2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="T2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="U2" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="V2" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X2" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y2" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="Z2" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA2" s="37" t="s">
+        <v>560</v>
+      </c>
+      <c r="AB2" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AC2" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AD2" s="37" t="s">
+        <v>561</v>
+      </c>
+      <c r="AE2" s="37" t="s">
+        <v>562</v>
+      </c>
+      <c r="AF2" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG2" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH2" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI2" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ2" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK2" s="38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AE3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF2" s="5" t="s">
+      <c r="AG3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AG2" s="5" t="s">
+      <c r="AH3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AH2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ2" s="5" t="s">
+      <c r="AI3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AK2" s="5" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AL2" s="5" t="s">
+      <c r="AK3" s="2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3303,1574 +3559,1574 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" customWidth="1"/>
-    <col min="2" max="14" width="9.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" style="1" customWidth="1"/>
+    <col min="2" max="14" width="9.6328125" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26" t="s">
+      <c r="G1" s="22"/>
+      <c r="H1" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26" t="s">
+      <c r="I1" s="22"/>
+      <c r="J1" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26" t="s">
+      <c r="K1" s="22"/>
+      <c r="L1" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26" t="s">
+      <c r="M1" s="22"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26" t="s">
+      <c r="C2" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="26"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="C3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="27" t="s">
+      <c r="D3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="27" t="s">
+      <c r="F3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="27" t="s">
+      <c r="H3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="J3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" s="27" t="s">
+      <c r="L3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="G34" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="I34" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="K34" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="K4" s="5" t="s">
+      <c r="M34" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="M4" s="5" t="s">
+      <c r="C35" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="E35" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="G35" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="I35" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="K35" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="K6" s="5" t="s">
+      <c r="M35" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="M6" s="5" t="s">
+      <c r="C36" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="E36" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="G36" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="I36" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="K36" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
-        <v>540</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
+      <c r="M36" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4888,230 +5144,229 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="46.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.90625" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="14"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+    <row r="1" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A1" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="17" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A2" s="7" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="B2" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="17" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+    <row r="4" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="16" t="s">
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="16" t="s">
+    <row r="7" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A7" s="12" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="16" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A8" s="12" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="16" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A9" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+    <row r="10" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A10" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="16" t="s">
+    <row r="11" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A11" s="12" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="B11" s="14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+    <row r="12" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A12" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="30"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="B12" s="14" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+    <row r="13" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A13" s="12" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="B13" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="30"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="30"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
+      <c r="B14" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="23"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A15" s="15"/>
+      <c r="B15" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B32" s="23"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="14.5" thickBot="1">
+      <c r="A16" s="15"/>
+      <c r="B16" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B33" s="33"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="24"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="34" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="14.5" thickBot="1">
+      <c r="A17" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B17" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="27.5" thickBot="1">
+      <c r="A18" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.5" thickBot="1">
+      <c r="A19" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="14.5" thickBot="1">
+      <c r="A20" s="15"/>
+      <c r="B20" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="26"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="27.5">
+      <c r="A25" s="18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="26"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="26"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="20"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="20"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="29"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="17"/>
+      <c r="B34" s="21"/>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5121,7 +5376,7 @@
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A35:B35"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\gitHome\pingdingshan\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="110" windowWidth="19400" windowHeight="7100"/>
+    <workbookView xWindow="600" yWindow="105" windowWidth="19395" windowHeight="7095"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t>${data.prodBrand}</t>
   </si>
   <si>
-    <t>${data.prodStage}</t>
-  </si>
-  <si>
     <t>${data.raiseType}</t>
   </si>
   <si>
@@ -2594,6 +2591,10 @@
   </si>
   <si>
     <t>增信机构类型</t>
+  </si>
+  <si>
+    <t>${data.prodStageToString}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2848,14 +2849,35 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -2877,27 +2899,6 @@
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3204,235 +3205,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK3"/>
-  <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.453125" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="15.6328125" style="2"/>
+    <col min="1" max="1" width="18.5" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="15.625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" customFormat="1" ht="249.75" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="22" t="s">
+        <v>555</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>556</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="C1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>557</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" s="32" t="s">
+      <c r="K1" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="L1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="T1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="U1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="V1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="W1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="X1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z1" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD1" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE1" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG1" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH1" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK1" s="23" t="s">
         <v>558</v>
       </c>
-      <c r="K1" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="M1" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="P1" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q1" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="R1" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="T1" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="U1" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="V1" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="W1" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="X1" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y1" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z1" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA1" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB1" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC1" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD1" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE1" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF1" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG1" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="AH1" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="AI1" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ1" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK1" s="33" t="s">
+    </row>
+    <row r="2" spans="1:37" s="27" customFormat="1" ht="26.1" customHeight="1">
+      <c r="A2" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="W2" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="27" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="2" spans="1:37" s="37" customFormat="1" ht="26" customHeight="1">
-      <c r="A2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="V2" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="X2" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="37" t="s">
+      <c r="AB2" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC2" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>560</v>
       </c>
-      <c r="AB2" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC2" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD2" s="37" t="s">
+      <c r="AE2" s="27" t="s">
         <v>561</v>
       </c>
-      <c r="AE2" s="37" t="s">
-        <v>562</v>
-      </c>
-      <c r="AF2" s="37" t="s">
+      <c r="AF2" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="AG2" s="37" t="s">
+      <c r="AG2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="AH2" s="38" t="s">
+      <c r="AH2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="AI2" s="38" t="s">
+      <c r="AI2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AJ2" s="38" t="s">
+      <c r="AJ2" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="AK2" s="38" t="s">
+      <c r="AK2" s="28" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3444,109 +3445,109 @@
         <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="S3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="V3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK3" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3559,1475 +3560,1475 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" style="1" customWidth="1"/>
-    <col min="2" max="14" width="9.6328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
+    <col min="2" max="14" width="9.625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="30"/>
+      <c r="J1" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22" t="s">
+      <c r="K1" s="30"/>
+      <c r="L1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="30"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="22"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="C3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="23" t="s">
+      <c r="E3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="23" t="s">
+      <c r="G3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" s="23" t="s">
+      <c r="I3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="L2" s="23" t="s">
+      <c r="K3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="I33" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="J33" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="H34" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="I34" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="J34" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="L34" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="I36" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="J36" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5130,11 +5131,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="L2:M2"/>
@@ -5143,6 +5139,11 @@
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5152,221 +5153,221 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="46.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.90625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="46.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1">
+    <row r="1" spans="1:4" ht="14.25" thickBot="1">
       <c r="A1" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A2" s="7" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1">
+    </row>
+    <row r="3" spans="1:4" ht="14.25" thickBot="1">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" thickBot="1">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1">
+    <row r="5" spans="1:4" ht="14.25" thickBot="1">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1">
+    <row r="6" spans="1:4" ht="14.25" thickBot="1">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A7" s="12" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A8" s="12" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="13" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A9" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A9" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="10" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A10" s="12" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A10" s="12" t="s">
+      <c r="B10" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="14" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A11" s="12" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A11" s="12" t="s">
+      <c r="B11" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A12" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A12" s="12" t="s">
+      <c r="B12" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="14" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A13" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A13" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="14" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A14" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="14.5" thickBot="1">
-      <c r="A14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.5" thickBot="1">
+    </row>
+    <row r="15" spans="1:4" ht="14.25" thickBot="1">
       <c r="A15" s="15"/>
       <c r="B15" s="13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.5" thickBot="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1">
       <c r="A16" s="15"/>
       <c r="B16" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A17" s="12" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.5" thickBot="1">
-      <c r="A17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B17" s="13" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A18" s="12" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="27.5" thickBot="1">
-      <c r="A18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="13" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A19" s="12" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.5" thickBot="1">
-      <c r="A19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="14.5" thickBot="1">
+    </row>
+    <row r="20" spans="1:2" ht="14.25" thickBot="1">
       <c r="A20" s="15"/>
       <c r="B20" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="32" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" s="26"/>
+      <c r="B22" s="33"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="27.5">
-      <c r="A25" s="18" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="34" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="27" t="s">
+      <c r="B26" s="33"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="26"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="B27" s="26"/>
+      <c r="B27" s="33"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="16"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B31" s="20"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="20"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="B32" s="20"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="B33" s="29"/>
+      <c r="B33" s="36"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17"/>
       <c r="B34" s="21"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="B35" s="31"/>
+      <c r="A35" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB88D02-2933-4F7C-A761-1ADEFE90FBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="105" windowWidth="19395" windowHeight="7095"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="570">
   <si>
     <t>发起机构代码</t>
   </si>
@@ -132,6 +133,9 @@
   </si>
   <si>
     <t>${data.prodBrand}</t>
+  </si>
+  <si>
+    <t>${data.prodStage}</t>
   </si>
   <si>
     <t>${data.raiseType}</t>
@@ -2593,15 +2597,38 @@
     <t>增信机构类型</t>
   </si>
   <si>
-    <t>${data.prodStageToString}</t>
+    <t>${data.cashManaCate}</t>
+  </si>
+  <si>
+    <t>${data.crossBorderFlag}</t>
+  </si>
+  <si>
+    <t>是否现金管理类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨境理财通标识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>样式：文本
+内容：中文名称  选项：是、否</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>${data.zjxtFlag}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>以财产权信托名义开展的资金信托标识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2688,6 +2715,11 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2870,14 +2902,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -2918,7 +2950,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2993,6 +3025,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3028,6 +3077,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3203,128 +3269,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK3"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AN3"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="15.625" style="2"/>
+    <col min="1" max="1" width="18.44140625" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="15.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" customFormat="1" ht="249.75" customHeight="1">
+    <row r="1" spans="1:40" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="P1" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="T1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="U1" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="J1" s="23" t="s">
-        <v>557</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="N1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="O1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="P1" s="22" t="s">
+      <c r="V1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="W1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="X1" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y1" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB1" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC1" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD1" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF1" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG1" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH1" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI1" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="Q1" s="24" t="s">
+      <c r="AJ1" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="R1" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="S1" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="T1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="U1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="V1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="W1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="X1" s="22" t="s">
+      <c r="AK1" s="23" t="s">
+        <v>559</v>
+      </c>
+      <c r="AL1" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="AM1" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="Z1" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB1" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC1" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD1" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE1" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF1" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="AG1" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH1" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK1" s="23" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" s="27" customFormat="1" ht="26.1" customHeight="1">
+      <c r="AN1" s="22" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="27" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -3404,7 +3479,7 @@
         <v>25</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AB2" s="27" t="s">
         <v>26</v>
@@ -3413,10 +3488,10 @@
         <v>27</v>
       </c>
       <c r="AD2" s="27" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AE2" s="27" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AF2" s="27" t="s">
         <v>28</v>
@@ -3436,8 +3511,17 @@
       <c r="AK2" s="28" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:37">
+      <c r="AL2" s="28" t="s">
+        <v>565</v>
+      </c>
+      <c r="AM2" s="28" t="s">
+        <v>566</v>
+      </c>
+      <c r="AN2" s="28" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -3445,109 +3529,118 @@
         <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>562</v>
+        <v>37</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="X3" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AI3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AE3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AK3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>50</v>
+      <c r="AL3" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -3558,1480 +3651,1480 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
-    <col min="2" max="14" width="9.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" customWidth="1"/>
+    <col min="2" max="14" width="9.6640625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30" t="s">
+      <c r="C1" s="29"/>
+      <c r="D1" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30" t="s">
+      <c r="I1" s="29"/>
+      <c r="J1" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="30"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="31" t="s">
+      <c r="K1" s="29"/>
+      <c r="L1" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="29" t="s">
-        <v>61</v>
+      <c r="M1" s="29"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="E3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="G3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="I3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="K3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="M3" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="M36" s="2" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -5045,7 +5138,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -5059,7 +5152,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -5073,7 +5166,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -5087,7 +5180,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -5101,7 +5194,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -5115,7 +5208,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -5131,6 +5224,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="L2:M2"/>
@@ -5139,11 +5237,6 @@
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5151,221 +5244,221 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="46.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.88671875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" thickBot="1">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" thickBot="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.25" thickBot="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" ht="14.25" thickBot="1">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:4" ht="14.25" thickBot="1">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" thickBot="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" thickBot="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B8" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A9" s="12" t="s">
-        <v>133</v>
-      </c>
       <c r="B9" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" thickBot="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="14.25" thickBot="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" thickBot="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.25" thickBot="1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="14.25" thickBot="1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.25" thickBot="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" thickBot="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.25" thickBot="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.25" thickBot="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.25" thickBot="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="14.25" thickBot="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B22" s="33"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B26" s="33"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B27" s="33"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B31" s="20"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B32" s="20"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="35" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B33" s="36"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="21"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B35" s="38"/>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB88D02-2933-4F7C-A761-1ADEFE90FBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -135,9 +134,6 @@
     <t>${data.prodBrand}</t>
   </si>
   <si>
-    <t>${data.prodStage}</t>
-  </si>
-  <si>
     <t>${data.raiseType}</t>
   </si>
   <si>
@@ -2623,12 +2619,16 @@
     <t>以财产权信托名义开展的资金信托标识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>${data.prodStageToString}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2950,7 +2950,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3025,23 +3025,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3077,23 +3060,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3269,137 +3235,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AN3"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="15.6640625" style="2"/>
+    <col min="1" max="1" width="18.5" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="15.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" customFormat="1" ht="249.75" customHeight="1">
       <c r="A1" s="22" t="s">
+        <v>555</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>556</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>557</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="L1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="T1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="U1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="V1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="W1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="X1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z1" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD1" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE1" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG1" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH1" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK1" s="23" t="s">
         <v>558</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="AL1" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="L1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="O1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="P1" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="R1" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="S1" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="T1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="U1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="V1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="W1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="X1" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y1" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z1" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB1" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC1" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD1" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE1" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF1" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG1" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="AH1" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="AI1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK1" s="23" t="s">
-        <v>559</v>
-      </c>
-      <c r="AL1" s="22" t="s">
-        <v>114</v>
-      </c>
       <c r="AM1" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AN1" s="22" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" s="27" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="27" customFormat="1" ht="26.1" customHeight="1">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -3479,7 +3445,7 @@
         <v>25</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AB2" s="27" t="s">
         <v>26</v>
@@ -3488,10 +3454,10 @@
         <v>27</v>
       </c>
       <c r="AD2" s="27" t="s">
+        <v>560</v>
+      </c>
+      <c r="AE2" s="27" t="s">
         <v>561</v>
-      </c>
-      <c r="AE2" s="27" t="s">
-        <v>562</v>
       </c>
       <c r="AF2" s="27" t="s">
         <v>28</v>
@@ -3512,16 +3478,16 @@
         <v>33</v>
       </c>
       <c r="AL2" s="28" t="s">
+        <v>564</v>
+      </c>
+      <c r="AM2" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="AM2" s="28" t="s">
-        <v>566</v>
-      </c>
       <c r="AN2" s="28" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -3529,118 +3495,118 @@
         <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="S3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="V3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AA3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="AL3" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="AM3" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="AM3" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="AN3" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -3651,1480 +3617,1480 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" customWidth="1"/>
-    <col min="2" max="14" width="9.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
+    <col min="2" max="14" width="9.625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>62</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>63</v>
       </c>
       <c r="C1" s="29"/>
       <c r="D1" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E1" s="29"/>
       <c r="F1" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G1" s="29"/>
       <c r="H1" s="29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I1" s="29"/>
       <c r="J1" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K1" s="29"/>
       <c r="L1" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="29"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="29"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="30" t="s">
+      <c r="C2" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="30" t="s">
+      <c r="C3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="30" t="s">
+      <c r="E3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="30" t="s">
+      <c r="G3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" s="30" t="s">
+      <c r="I3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="L2" s="30" t="s">
+      <c r="K3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="L4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="D6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="D7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="L11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="D13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="L17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="L18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="L19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="L20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="L21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="L22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="L23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="L24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="L25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="D26" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="L26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="D27" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="L27" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="D28" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="L28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="D29" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="L29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="D30" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="L30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="D31" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="L31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="D32" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="L32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="D33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="L33" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="D34" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="L34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="D35" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="L35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="I36" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="J36" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="L36" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:13">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -5138,7 +5104,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -5152,7 +5118,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -5166,7 +5132,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -5180,7 +5146,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -5194,7 +5160,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -5208,7 +5174,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -5244,221 +5210,221 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="46.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="14.25" thickBot="1">
       <c r="A1" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A2" s="7" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" ht="14.25" thickBot="1">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" thickBot="1">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="14.25" thickBot="1">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="14.25" thickBot="1">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A7" s="12" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A8" s="12" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="13" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A9" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="10" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A10" s="12" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="B10" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="14" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A11" s="12" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="B11" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A12" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="B12" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="14" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A13" s="12" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="14" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A14" s="12" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" ht="14.25" thickBot="1">
       <c r="A15" s="15"/>
       <c r="B15" s="13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1">
       <c r="A16" s="15"/>
       <c r="B16" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A17" s="12" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B17" s="13" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A18" s="12" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="13" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A19" s="12" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2" ht="14.25" thickBot="1">
       <c r="A20" s="15"/>
       <c r="B20" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="16" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" s="32" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
+      <c r="B22" s="33"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B22" s="33"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="34" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+      <c r="B26" s="33"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="33"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
+      <c r="B27" s="33"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="33"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="B31" s="20"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B31" s="20"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="B32" s="20"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="B32" s="20"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
-        <v>164</v>
-      </c>
       <c r="B33" s="36"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="17"/>
       <c r="B34" s="21"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" s="38"/>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\GZYH\zgbszz-guangzhouyinghang\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D06683-63D1-4D13-966E-A14AA7F51236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -2599,10 +2600,6 @@
     <t>${data.crossBorderFlag}</t>
   </si>
   <si>
-    <t>是否现金管理类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>跨境理财通标识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2621,14 +2618,18 @@
   </si>
   <si>
     <t>${data.prodStageToString}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现金管理类产品标识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2902,14 +2903,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -2950,7 +2951,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3025,6 +3026,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3060,6 +3078,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3235,15 +3270,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AN3"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="15.625" style="2"/>
+    <col min="1" max="1" width="18.44140625" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="15.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" customFormat="1" ht="249.75" customHeight="1">
+    <row r="1" spans="1:40" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>555</v>
       </c>
@@ -3362,10 +3397,10 @@
         <v>113</v>
       </c>
       <c r="AN1" s="22" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" s="27" customFormat="1" ht="26.1" customHeight="1">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="27" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -3478,16 +3513,16 @@
         <v>33</v>
       </c>
       <c r="AL2" s="28" t="s">
+        <v>569</v>
+      </c>
+      <c r="AM2" s="28" t="s">
         <v>564</v>
       </c>
-      <c r="AM2" s="28" t="s">
-        <v>565</v>
-      </c>
       <c r="AN2" s="28" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -3501,7 +3536,7 @@
         <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>38</v>
@@ -3606,7 +3641,7 @@
         <v>563</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -3617,87 +3652,87 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
-    <col min="2" max="14" width="9.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" customWidth="1"/>
+    <col min="2" max="14" width="9.6640625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29" t="s">
+      <c r="I1" s="30"/>
+      <c r="J1" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29" t="s">
+      <c r="K1" s="30"/>
+      <c r="L1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="29"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="31" t="s">
+      <c r="M1" s="30"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="M2" s="31" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="31" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -3737,7 +3772,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>71</v>
       </c>
@@ -3778,7 +3813,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>72</v>
       </c>
@@ -3819,7 +3854,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3860,7 +3895,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -3901,7 +3936,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>75</v>
       </c>
@@ -3942,7 +3977,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>76</v>
       </c>
@@ -3983,7 +4018,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>77</v>
       </c>
@@ -4024,7 +4059,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>78</v>
       </c>
@@ -4065,7 +4100,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
@@ -4106,7 +4141,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>80</v>
       </c>
@@ -4147,7 +4182,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>81</v>
       </c>
@@ -4188,7 +4223,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>82</v>
       </c>
@@ -4229,7 +4264,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>83</v>
       </c>
@@ -4270,7 +4305,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>84</v>
       </c>
@@ -4311,7 +4346,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>85</v>
       </c>
@@ -4352,7 +4387,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>86</v>
       </c>
@@ -4393,7 +4428,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>87</v>
       </c>
@@ -4434,7 +4469,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>88</v>
       </c>
@@ -4475,7 +4510,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>89</v>
       </c>
@@ -4516,7 +4551,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>90</v>
       </c>
@@ -4557,7 +4592,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>91</v>
       </c>
@@ -4598,7 +4633,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>92</v>
       </c>
@@ -4639,7 +4674,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>93</v>
       </c>
@@ -4680,7 +4715,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -4721,7 +4756,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>95</v>
       </c>
@@ -4762,7 +4797,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>96</v>
       </c>
@@ -4803,7 +4838,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>97</v>
       </c>
@@ -4844,7 +4879,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>98</v>
       </c>
@@ -4885,7 +4920,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>99</v>
       </c>
@@ -4926,7 +4961,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>100</v>
       </c>
@@ -4967,7 +5002,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>101</v>
       </c>
@@ -5008,7 +5043,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>102</v>
       </c>
@@ -5049,7 +5084,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>103</v>
       </c>
@@ -5090,7 +5125,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -5104,7 +5139,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -5118,7 +5153,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -5132,7 +5167,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -5146,7 +5181,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -5160,7 +5195,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -5174,7 +5209,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -5190,11 +5225,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="L2:M2"/>
@@ -5203,6 +5233,11 @@
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5210,21 +5245,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="46.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.88671875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" thickBot="1">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>125</v>
       </c>
@@ -5232,33 +5267,33 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.25" thickBot="1">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.25" thickBot="1">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
         <v>128</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" ht="14.25" thickBot="1">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
         <v>129</v>
       </c>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:4" ht="14.25" thickBot="1">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.25" thickBot="1">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>131</v>
       </c>
@@ -5266,7 +5301,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="14.25" thickBot="1">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>133</v>
       </c>
@@ -5274,7 +5309,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.25" thickBot="1">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>133</v>
       </c>
@@ -5282,7 +5317,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="14.25" thickBot="1">
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>136</v>
       </c>
@@ -5290,7 +5325,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="14.25" thickBot="1">
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>138</v>
       </c>
@@ -5298,7 +5333,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="14.25" thickBot="1">
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>140</v>
       </c>
@@ -5306,7 +5341,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="14.25" thickBot="1">
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>142</v>
       </c>
@@ -5314,7 +5349,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="14.25" thickBot="1">
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>144</v>
       </c>
@@ -5322,19 +5357,19 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="14.25" thickBot="1">
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15" s="13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.25" thickBot="1">
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="13" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.25" thickBot="1">
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>148</v>
       </c>
@@ -5342,7 +5377,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.25" thickBot="1">
+    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>150</v>
       </c>
@@ -5350,7 +5385,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.25" thickBot="1">
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>152</v>
       </c>
@@ -5358,71 +5393,71 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.25" thickBot="1">
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="13" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>156</v>
       </c>
       <c r="B22" s="33"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
         <v>159</v>
       </c>
       <c r="B26" s="33"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
         <v>160</v>
       </c>
       <c r="B27" s="33"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>161</v>
       </c>
       <c r="B31" s="20"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>162</v>
       </c>
       <c r="B32" s="20"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="35" t="s">
         <v>163</v>
       </c>
       <c r="B33" s="36"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="21"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
         <v>164</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_PrdBaseinfo_CNY.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\GZYH\zgbszz-guangzhouyinghang\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\feature3.0.6\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D06683-63D1-4D13-966E-A14AA7F51236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
@@ -75,9 +74,6 @@
     <t>募集结束日期</t>
   </si>
   <si>
-    <t>提前终止权标识</t>
-  </si>
-  <si>
     <t>客户赎回权标识</t>
   </si>
   <si>
@@ -106,9 +102,6 @@
   </si>
   <si>
     <t>兑付收益币种</t>
-  </si>
-  <si>
-    <t>增信形式</t>
   </si>
   <si>
     <t>受托职责</t>
@@ -2591,9 +2584,6 @@
     <t>客户类型</t>
   </si>
   <si>
-    <t>增信机构类型</t>
-  </si>
-  <si>
     <t>${data.cashManaCate}</t>
   </si>
   <si>
@@ -2622,14 +2612,26 @@
   </si>
   <si>
     <t>现金管理类产品标识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发行机构提前终止权标识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品增信机构类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品增信形式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2903,14 +2905,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -2951,7 +2953,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3026,23 +3028,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -3078,23 +3063,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3270,137 +3238,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AN3"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="15.6640625" style="2"/>
+    <col min="1" max="1" width="18.5" style="2" customWidth="1"/>
+    <col min="2" max="17" width="15.625" style="2"/>
+    <col min="18" max="18" width="25.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="15.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" customFormat="1" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" customFormat="1" ht="249.75" customHeight="1">
       <c r="A1" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>555</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="K1" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="T1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="U1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="V1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="W1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="X1" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y1" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z1" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD1" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE1" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF1" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG1" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK1" s="23" t="s">
         <v>556</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="22" t="s">
+      <c r="AL1" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="23" t="s">
-        <v>557</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="N1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="O1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="P1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="R1" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="S1" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="T1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="U1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="V1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="W1" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="X1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z1" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB1" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC1" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD1" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE1" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF1" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="AG1" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH1" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ1" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK1" s="23" t="s">
-        <v>558</v>
-      </c>
-      <c r="AL1" s="22" t="s">
-        <v>113</v>
-      </c>
       <c r="AM1" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AN1" s="22" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" s="27" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="27" customFormat="1" ht="26.1" customHeight="1">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -3453,195 +3423,195 @@
         <v>16</v>
       </c>
       <c r="R2" s="27" t="s">
+        <v>567</v>
+      </c>
+      <c r="S2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="T2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
+        <v>557</v>
+      </c>
+      <c r="AB2" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD2" s="27" t="s">
+        <v>558</v>
+      </c>
+      <c r="AE2" s="27" t="s">
+        <v>568</v>
+      </c>
+      <c r="AF2" s="27" t="s">
+        <v>569</v>
+      </c>
+      <c r="AG2" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH2" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI2" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ2" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AK2" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL2" s="28" t="s">
+        <v>566</v>
+      </c>
+      <c r="AM2" s="28" t="s">
+        <v>561</v>
+      </c>
+      <c r="AN2" s="28" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL3" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="AB2" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC2" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD2" s="27" t="s">
+      <c r="AM3" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="AE2" s="27" t="s">
-        <v>561</v>
-      </c>
-      <c r="AF2" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG2" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH2" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI2" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ2" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK2" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL2" s="28" t="s">
-        <v>569</v>
-      </c>
-      <c r="AM2" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="AN2" s="28" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AN3" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -3652,1480 +3622,1480 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" customWidth="1"/>
-    <col min="2" max="14" width="9.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
+    <col min="2" max="14" width="9.625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30" t="s">
+      <c r="I1" s="29"/>
+      <c r="J1" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30" t="s">
+      <c r="K1" s="29"/>
+      <c r="L1" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30" t="s">
+      <c r="M1" s="29"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30" t="s">
+      <c r="C2" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="30"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="31" t="s">
+      <c r="C3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="31" t="s">
+      <c r="D3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="31" t="s">
+      <c r="F3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="31" t="s">
+      <c r="H3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="31" t="s">
+      <c r="J3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="31" t="s">
+      <c r="L3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="F6" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="B7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="B8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="B14" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="B15" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="B30" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="B31" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="B32" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="B33" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="B34" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="B35" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="J35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="I36" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="J36" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:13">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -5139,7 +5109,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -5153,7 +5123,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -5167,7 +5137,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -5181,7 +5151,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -5195,7 +5165,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -5209,7 +5179,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -5225,6 +5195,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="L2:M2"/>
@@ -5233,11 +5208,6 @@
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5245,221 +5215,221 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="46.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.875" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="14.25" thickBot="1">
       <c r="A1" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A2" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="14.25" thickBot="1">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" thickBot="1">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="14.25" thickBot="1">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="14.25" thickBot="1">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+    <row r="8" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A8" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B8" s="13" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+    <row r="9" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A9" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="13" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A10" s="12" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A11" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B11" s="14" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+    <row r="12" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A12" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B12" s="14" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+    <row r="13" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A13" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B13" s="14" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+    <row r="14" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A14" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="14.25" thickBot="1">
       <c r="A15" s="15"/>
       <c r="B15" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1">
       <c r="A16" s="15"/>
       <c r="B16" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A17" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+    <row r="18" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A18" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B18" s="13" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
+    <row r="19" spans="1:2" ht="14.25" thickBot="1">
+      <c r="A19" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B19" s="13" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="14.25" thickBot="1">
       <c r="A20" s="15"/>
       <c r="B20" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="32" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="B22" s="33"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="17" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="33"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="34" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="B26" s="33"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="34" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+      <c r="B27" s="33"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="33"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
+      <c r="B31" s="20"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="B27" s="33"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="B32" s="20"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="B31" s="20"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" s="20"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
-        <v>163</v>
-      </c>
       <c r="B33" s="36"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="17"/>
       <c r="B34" s="21"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="37" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B35" s="38"/>
     </row>
